--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_Demand.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_Demand.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.85546875" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -738,88 +738,88 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>499.71</v>
+        <v>469.23</v>
       </c>
       <c r="J2" t="n">
-        <v>542.73</v>
+        <v>478.61</v>
       </c>
       <c r="K2" t="n">
-        <v>585.75</v>
+        <v>488</v>
       </c>
       <c r="L2" t="n">
-        <v>631.35</v>
+        <v>497.38</v>
       </c>
       <c r="M2" t="n">
-        <v>676.95</v>
+        <v>506.77</v>
       </c>
       <c r="N2" t="n">
-        <v>722.54</v>
+        <v>516.15</v>
       </c>
       <c r="O2" t="n">
-        <v>768.14</v>
+        <v>525.54</v>
       </c>
       <c r="P2" t="n">
-        <v>813.74</v>
+        <v>534.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>860.42</v>
+        <v>544.3099999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>907.11</v>
+        <v>553.6900000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>953.79</v>
+        <v>563.08</v>
       </c>
       <c r="T2" t="n">
-        <v>1000.48</v>
+        <v>572.46</v>
       </c>
       <c r="U2" t="n">
-        <v>1047.16</v>
+        <v>581.85</v>
       </c>
       <c r="V2" t="n">
-        <v>1094.98</v>
+        <v>591.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1142.8</v>
+        <v>600.61</v>
       </c>
       <c r="X2" t="n">
-        <v>1190.62</v>
+        <v>610</v>
       </c>
       <c r="Y2" t="n">
-        <v>1238.44</v>
+        <v>619.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>1286.25</v>
+        <v>628.77</v>
       </c>
       <c r="AA2" t="n">
-        <v>1334.01</v>
+        <v>638.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>1381.76</v>
+        <v>647.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>1429.51</v>
+        <v>656.92</v>
       </c>
       <c r="AD2" t="n">
-        <v>1477.26</v>
+        <v>666.3099999999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>1525.02</v>
+        <v>675.6900000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>1574.01</v>
+        <v>685.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1623.01</v>
+        <v>694.46</v>
       </c>
       <c r="AH2" t="n">
-        <v>1672</v>
+        <v>703.85</v>
       </c>
       <c r="AI2" t="n">
-        <v>1721</v>
+        <v>713.23</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1769.99</v>
+        <v>722.61</v>
       </c>
     </row>
     <row r="3">
@@ -862,88 +862,88 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>12.58</v>
+        <v>3.87</v>
       </c>
       <c r="J3" t="n">
-        <v>14.11</v>
+        <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>15.66</v>
+        <v>4.03</v>
       </c>
       <c r="L3" t="n">
-        <v>17.32</v>
+        <v>4.11</v>
       </c>
       <c r="M3" t="n">
-        <v>18.97</v>
+        <v>4.18</v>
       </c>
       <c r="N3" t="n">
-        <v>20.62</v>
+        <v>4.26</v>
       </c>
       <c r="O3" t="n">
-        <v>22.27</v>
+        <v>4.34</v>
       </c>
       <c r="P3" t="n">
-        <v>23.95</v>
+        <v>4.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.73</v>
+        <v>4.49</v>
       </c>
       <c r="R3" t="n">
-        <v>27.51</v>
+        <v>4.57</v>
       </c>
       <c r="S3" t="n">
-        <v>29.28</v>
+        <v>4.65</v>
       </c>
       <c r="T3" t="n">
-        <v>31.09</v>
+        <v>4.73</v>
       </c>
       <c r="U3" t="n">
-        <v>32.86</v>
+        <v>4.8</v>
       </c>
       <c r="V3" t="n">
-        <v>34.84</v>
+        <v>4.88</v>
       </c>
       <c r="W3" t="n">
-        <v>36.82</v>
+        <v>4.96</v>
       </c>
       <c r="X3" t="n">
-        <v>38.8</v>
+        <v>5.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>40.78</v>
+        <v>5.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>42.75</v>
+        <v>5.19</v>
       </c>
       <c r="AA3" t="n">
-        <v>44.93</v>
+        <v>5.27</v>
       </c>
       <c r="AB3" t="n">
-        <v>47.11</v>
+        <v>5.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>49.29</v>
+        <v>5.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>51.47</v>
+        <v>5.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>53.64</v>
+        <v>5.58</v>
       </c>
       <c r="AF3" t="n">
-        <v>56</v>
+        <v>5.66</v>
       </c>
       <c r="AG3" t="n">
-        <v>58.35</v>
+        <v>5.73</v>
       </c>
       <c r="AH3" t="n">
-        <v>60.7</v>
+        <v>5.81</v>
       </c>
       <c r="AI3" t="n">
-        <v>63.06</v>
+        <v>5.89</v>
       </c>
       <c r="AJ3" t="n">
-        <v>65.41</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="4">
@@ -1606,88 +1606,88 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>47.48</v>
+        <v>290.09</v>
       </c>
       <c r="J9" t="n">
-        <v>47.48</v>
+        <v>295.89</v>
       </c>
       <c r="K9" t="n">
-        <v>47.48</v>
+        <v>301.69</v>
       </c>
       <c r="L9" t="n">
-        <v>54.22</v>
+        <v>307.49</v>
       </c>
       <c r="M9" t="n">
-        <v>60.95</v>
+        <v>313.3</v>
       </c>
       <c r="N9" t="n">
-        <v>67.69</v>
+        <v>319.1</v>
       </c>
       <c r="O9" t="n">
-        <v>74.42</v>
+        <v>324.9</v>
       </c>
       <c r="P9" t="n">
-        <v>81.15000000000001</v>
+        <v>330.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>88.8</v>
+        <v>336.5</v>
       </c>
       <c r="R9" t="n">
-        <v>96.45999999999999</v>
+        <v>342.31</v>
       </c>
       <c r="S9" t="n">
-        <v>104.11</v>
+        <v>348.11</v>
       </c>
       <c r="T9" t="n">
-        <v>111.76</v>
+        <v>353.91</v>
       </c>
       <c r="U9" t="n">
-        <v>119.41</v>
+        <v>359.71</v>
       </c>
       <c r="V9" t="n">
-        <v>127.6</v>
+        <v>365.51</v>
       </c>
       <c r="W9" t="n">
-        <v>135.78</v>
+        <v>371.31</v>
       </c>
       <c r="X9" t="n">
-        <v>143.96</v>
+        <v>377.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>152.15</v>
+        <v>382.92</v>
       </c>
       <c r="Z9" t="n">
-        <v>160.33</v>
+        <v>388.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>168.97</v>
+        <v>394.52</v>
       </c>
       <c r="AB9" t="n">
-        <v>177.6</v>
+        <v>400.32</v>
       </c>
       <c r="AC9" t="n">
-        <v>186.23</v>
+        <v>406.13</v>
       </c>
       <c r="AD9" t="n">
-        <v>194.87</v>
+        <v>411.93</v>
       </c>
       <c r="AE9" t="n">
-        <v>203.5</v>
+        <v>417.73</v>
       </c>
       <c r="AF9" t="n">
-        <v>212.6</v>
+        <v>423.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>221.7</v>
+        <v>429.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>230.79</v>
+        <v>435.13</v>
       </c>
       <c r="AI9" t="n">
-        <v>239.89</v>
+        <v>440.94</v>
       </c>
       <c r="AJ9" t="n">
-        <v>248.99</v>
+        <v>446.74</v>
       </c>
     </row>
     <row r="10">
@@ -1730,88 +1730,88 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>47.48</v>
+        <v>2549.23</v>
       </c>
       <c r="J10" t="n">
-        <v>47.48</v>
+        <v>2600.21</v>
       </c>
       <c r="K10" t="n">
-        <v>47.48</v>
+        <v>2651.2</v>
       </c>
       <c r="L10" t="n">
-        <v>54.22</v>
+        <v>2702.18</v>
       </c>
       <c r="M10" t="n">
-        <v>60.95</v>
+        <v>2753.17</v>
       </c>
       <c r="N10" t="n">
-        <v>67.69</v>
+        <v>2804.15</v>
       </c>
       <c r="O10" t="n">
-        <v>74.42</v>
+        <v>2855.14</v>
       </c>
       <c r="P10" t="n">
-        <v>81.15000000000001</v>
+        <v>2906.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>88.8</v>
+        <v>2957.11</v>
       </c>
       <c r="R10" t="n">
-        <v>96.45999999999999</v>
+        <v>3008.09</v>
       </c>
       <c r="S10" t="n">
-        <v>104.11</v>
+        <v>3059.07</v>
       </c>
       <c r="T10" t="n">
-        <v>111.76</v>
+        <v>3110.06</v>
       </c>
       <c r="U10" t="n">
-        <v>119.41</v>
+        <v>3161.04</v>
       </c>
       <c r="V10" t="n">
-        <v>127.6</v>
+        <v>3212.03</v>
       </c>
       <c r="W10" t="n">
-        <v>135.78</v>
+        <v>3263.01</v>
       </c>
       <c r="X10" t="n">
-        <v>143.96</v>
+        <v>3314</v>
       </c>
       <c r="Y10" t="n">
-        <v>152.15</v>
+        <v>3364.98</v>
       </c>
       <c r="Z10" t="n">
-        <v>160.33</v>
+        <v>3415.97</v>
       </c>
       <c r="AA10" t="n">
-        <v>168.97</v>
+        <v>3466.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>177.6</v>
+        <v>3517.94</v>
       </c>
       <c r="AC10" t="n">
-        <v>186.23</v>
+        <v>3568.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>194.87</v>
+        <v>3619.91</v>
       </c>
       <c r="AE10" t="n">
-        <v>203.5</v>
+        <v>3670.89</v>
       </c>
       <c r="AF10" t="n">
-        <v>212.6</v>
+        <v>3721.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>221.7</v>
+        <v>3772.86</v>
       </c>
       <c r="AH10" t="n">
-        <v>230.79</v>
+        <v>3823.84</v>
       </c>
       <c r="AI10" t="n">
-        <v>239.89</v>
+        <v>3874.83</v>
       </c>
       <c r="AJ10" t="n">
-        <v>248.99</v>
+        <v>3925.81</v>
       </c>
     </row>
     <row r="11">
@@ -1854,88 +1854,212 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>18.94</v>
+        <v>302.39</v>
       </c>
       <c r="J11" t="n">
-        <v>18.94</v>
+        <v>308.44</v>
       </c>
       <c r="K11" t="n">
-        <v>18.94</v>
+        <v>314.49</v>
       </c>
       <c r="L11" t="n">
-        <v>18.94</v>
+        <v>320.54</v>
       </c>
       <c r="M11" t="n">
-        <v>18.94</v>
+        <v>326.58</v>
       </c>
       <c r="N11" t="n">
-        <v>18.94</v>
+        <v>332.63</v>
       </c>
       <c r="O11" t="n">
-        <v>18.94</v>
+        <v>338.68</v>
       </c>
       <c r="P11" t="n">
-        <v>18.94</v>
+        <v>344.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>26.1</v>
+        <v>350.78</v>
       </c>
       <c r="R11" t="n">
-        <v>33.26</v>
+        <v>356.82</v>
       </c>
       <c r="S11" t="n">
-        <v>40.42</v>
+        <v>362.87</v>
       </c>
       <c r="T11" t="n">
-        <v>47.58</v>
+        <v>368.92</v>
       </c>
       <c r="U11" t="n">
-        <v>54.74</v>
+        <v>374.97</v>
       </c>
       <c r="V11" t="n">
-        <v>63.84</v>
+        <v>381.01</v>
       </c>
       <c r="W11" t="n">
-        <v>72.94</v>
+        <v>387.06</v>
       </c>
       <c r="X11" t="n">
-        <v>82.04000000000001</v>
+        <v>393.11</v>
       </c>
       <c r="Y11" t="n">
-        <v>91.14</v>
+        <v>399.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>100.24</v>
+        <v>405.21</v>
       </c>
       <c r="AA11" t="n">
-        <v>110.25</v>
+        <v>411.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>120.27</v>
+        <v>417.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>130.28</v>
+        <v>423.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>140.3</v>
+        <v>429.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>150.31</v>
+        <v>435.45</v>
       </c>
       <c r="AF11" t="n">
-        <v>161.31</v>
+        <v>441.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>172.3</v>
+        <v>447.54</v>
       </c>
       <c r="AH11" t="n">
-        <v>183.29</v>
+        <v>453.59</v>
       </c>
       <c r="AI11" t="n">
-        <v>194.29</v>
+        <v>459.64</v>
       </c>
       <c r="AJ11" t="n">
-        <v>205.28</v>
+        <v>465.68</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ELCINDXX02</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Output demand of transmission lines in India</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>not needed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>not needed</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>not needed</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>User defined</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>43.08</v>
+      </c>
+      <c r="J12" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="K12" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="M12" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="N12" t="n">
+        <v>47.39</v>
+      </c>
+      <c r="O12" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="R12" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="S12" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="U12" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="V12" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="W12" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="X12" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>59.45</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>60.31</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>61.17</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>62.03</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>63.76</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>65.48</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>66.34</v>
       </c>
     </row>
   </sheetData>

--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_Demand.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_Demand.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.85546875" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -738,88 +738,88 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>469.23</v>
+        <v>499.71</v>
       </c>
       <c r="J2" t="n">
-        <v>478.61</v>
+        <v>542.73</v>
       </c>
       <c r="K2" t="n">
-        <v>488</v>
+        <v>585.75</v>
       </c>
       <c r="L2" t="n">
-        <v>497.38</v>
+        <v>631.35</v>
       </c>
       <c r="M2" t="n">
-        <v>506.77</v>
+        <v>676.95</v>
       </c>
       <c r="N2" t="n">
-        <v>516.15</v>
+        <v>722.54</v>
       </c>
       <c r="O2" t="n">
-        <v>525.54</v>
+        <v>768.14</v>
       </c>
       <c r="P2" t="n">
-        <v>534.92</v>
+        <v>813.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>544.3099999999999</v>
+        <v>860.42</v>
       </c>
       <c r="R2" t="n">
-        <v>553.6900000000001</v>
+        <v>907.11</v>
       </c>
       <c r="S2" t="n">
-        <v>563.08</v>
+        <v>953.79</v>
       </c>
       <c r="T2" t="n">
-        <v>572.46</v>
+        <v>1000.48</v>
       </c>
       <c r="U2" t="n">
-        <v>581.85</v>
+        <v>1047.16</v>
       </c>
       <c r="V2" t="n">
-        <v>591.23</v>
+        <v>1094.98</v>
       </c>
       <c r="W2" t="n">
-        <v>600.61</v>
+        <v>1142.8</v>
       </c>
       <c r="X2" t="n">
-        <v>610</v>
+        <v>1190.62</v>
       </c>
       <c r="Y2" t="n">
-        <v>619.38</v>
+        <v>1238.44</v>
       </c>
       <c r="Z2" t="n">
-        <v>628.77</v>
+        <v>1286.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>638.15</v>
+        <v>1334.01</v>
       </c>
       <c r="AB2" t="n">
-        <v>647.54</v>
+        <v>1381.76</v>
       </c>
       <c r="AC2" t="n">
-        <v>656.92</v>
+        <v>1429.51</v>
       </c>
       <c r="AD2" t="n">
-        <v>666.3099999999999</v>
+        <v>1477.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>675.6900000000001</v>
+        <v>1525.02</v>
       </c>
       <c r="AF2" t="n">
-        <v>685.08</v>
+        <v>1574.01</v>
       </c>
       <c r="AG2" t="n">
-        <v>694.46</v>
+        <v>1623.01</v>
       </c>
       <c r="AH2" t="n">
-        <v>703.85</v>
+        <v>1672</v>
       </c>
       <c r="AI2" t="n">
-        <v>713.23</v>
+        <v>1721</v>
       </c>
       <c r="AJ2" t="n">
-        <v>722.61</v>
+        <v>1769.99</v>
       </c>
     </row>
     <row r="3">
@@ -862,88 +862,88 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3.87</v>
+        <v>12.58</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>14.11</v>
       </c>
       <c r="K3" t="n">
-        <v>4.03</v>
+        <v>15.66</v>
       </c>
       <c r="L3" t="n">
-        <v>4.11</v>
+        <v>17.32</v>
       </c>
       <c r="M3" t="n">
-        <v>4.18</v>
+        <v>18.97</v>
       </c>
       <c r="N3" t="n">
-        <v>4.26</v>
+        <v>20.62</v>
       </c>
       <c r="O3" t="n">
-        <v>4.34</v>
+        <v>22.27</v>
       </c>
       <c r="P3" t="n">
-        <v>4.42</v>
+        <v>23.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.49</v>
+        <v>25.73</v>
       </c>
       <c r="R3" t="n">
-        <v>4.57</v>
+        <v>27.51</v>
       </c>
       <c r="S3" t="n">
-        <v>4.65</v>
+        <v>29.28</v>
       </c>
       <c r="T3" t="n">
-        <v>4.73</v>
+        <v>31.09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.8</v>
+        <v>32.86</v>
       </c>
       <c r="V3" t="n">
-        <v>4.88</v>
+        <v>34.84</v>
       </c>
       <c r="W3" t="n">
-        <v>4.96</v>
+        <v>36.82</v>
       </c>
       <c r="X3" t="n">
-        <v>5.04</v>
+        <v>38.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.11</v>
+        <v>40.78</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.19</v>
+        <v>42.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.27</v>
+        <v>44.93</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.35</v>
+        <v>47.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.42</v>
+        <v>49.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.5</v>
+        <v>51.47</v>
       </c>
       <c r="AE3" t="n">
-        <v>5.58</v>
+        <v>53.64</v>
       </c>
       <c r="AF3" t="n">
-        <v>5.66</v>
+        <v>56</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.73</v>
+        <v>58.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>5.81</v>
+        <v>60.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.89</v>
+        <v>63.06</v>
       </c>
       <c r="AJ3" t="n">
-        <v>5.97</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="4">
@@ -1606,88 +1606,88 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>290.09</v>
+        <v>47.48</v>
       </c>
       <c r="J9" t="n">
-        <v>295.89</v>
+        <v>47.48</v>
       </c>
       <c r="K9" t="n">
-        <v>301.69</v>
+        <v>47.48</v>
       </c>
       <c r="L9" t="n">
-        <v>307.49</v>
+        <v>54.22</v>
       </c>
       <c r="M9" t="n">
-        <v>313.3</v>
+        <v>60.95</v>
       </c>
       <c r="N9" t="n">
-        <v>319.1</v>
+        <v>67.69</v>
       </c>
       <c r="O9" t="n">
-        <v>324.9</v>
+        <v>74.42</v>
       </c>
       <c r="P9" t="n">
-        <v>330.7</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>336.5</v>
+        <v>88.8</v>
       </c>
       <c r="R9" t="n">
-        <v>342.31</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>348.11</v>
+        <v>104.11</v>
       </c>
       <c r="T9" t="n">
-        <v>353.91</v>
+        <v>111.76</v>
       </c>
       <c r="U9" t="n">
-        <v>359.71</v>
+        <v>119.41</v>
       </c>
       <c r="V9" t="n">
-        <v>365.51</v>
+        <v>127.6</v>
       </c>
       <c r="W9" t="n">
-        <v>371.31</v>
+        <v>135.78</v>
       </c>
       <c r="X9" t="n">
-        <v>377.12</v>
+        <v>143.96</v>
       </c>
       <c r="Y9" t="n">
-        <v>382.92</v>
+        <v>152.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>388.72</v>
+        <v>160.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>394.52</v>
+        <v>168.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>400.32</v>
+        <v>177.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>406.13</v>
+        <v>186.23</v>
       </c>
       <c r="AD9" t="n">
-        <v>411.93</v>
+        <v>194.87</v>
       </c>
       <c r="AE9" t="n">
-        <v>417.73</v>
+        <v>203.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>423.53</v>
+        <v>212.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>429.33</v>
+        <v>221.7</v>
       </c>
       <c r="AH9" t="n">
-        <v>435.13</v>
+        <v>230.79</v>
       </c>
       <c r="AI9" t="n">
-        <v>440.94</v>
+        <v>239.89</v>
       </c>
       <c r="AJ9" t="n">
-        <v>446.74</v>
+        <v>248.99</v>
       </c>
     </row>
     <row r="10">
@@ -1730,88 +1730,88 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2549.23</v>
+        <v>47.48</v>
       </c>
       <c r="J10" t="n">
-        <v>2600.21</v>
+        <v>47.48</v>
       </c>
       <c r="K10" t="n">
-        <v>2651.2</v>
+        <v>47.48</v>
       </c>
       <c r="L10" t="n">
-        <v>2702.18</v>
+        <v>54.22</v>
       </c>
       <c r="M10" t="n">
-        <v>2753.17</v>
+        <v>60.95</v>
       </c>
       <c r="N10" t="n">
-        <v>2804.15</v>
+        <v>67.69</v>
       </c>
       <c r="O10" t="n">
-        <v>2855.14</v>
+        <v>74.42</v>
       </c>
       <c r="P10" t="n">
-        <v>2906.12</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>2957.11</v>
+        <v>88.8</v>
       </c>
       <c r="R10" t="n">
-        <v>3008.09</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>3059.07</v>
+        <v>104.11</v>
       </c>
       <c r="T10" t="n">
-        <v>3110.06</v>
+        <v>111.76</v>
       </c>
       <c r="U10" t="n">
-        <v>3161.04</v>
+        <v>119.41</v>
       </c>
       <c r="V10" t="n">
-        <v>3212.03</v>
+        <v>127.6</v>
       </c>
       <c r="W10" t="n">
-        <v>3263.01</v>
+        <v>135.78</v>
       </c>
       <c r="X10" t="n">
-        <v>3314</v>
+        <v>143.96</v>
       </c>
       <c r="Y10" t="n">
-        <v>3364.98</v>
+        <v>152.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>3415.97</v>
+        <v>160.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>3466.95</v>
+        <v>168.97</v>
       </c>
       <c r="AB10" t="n">
-        <v>3517.94</v>
+        <v>177.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3568.92</v>
+        <v>186.23</v>
       </c>
       <c r="AD10" t="n">
-        <v>3619.91</v>
+        <v>194.87</v>
       </c>
       <c r="AE10" t="n">
-        <v>3670.89</v>
+        <v>203.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>3721.87</v>
+        <v>212.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>3772.86</v>
+        <v>221.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>3823.84</v>
+        <v>230.79</v>
       </c>
       <c r="AI10" t="n">
-        <v>3874.83</v>
+        <v>239.89</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3925.81</v>
+        <v>248.99</v>
       </c>
     </row>
     <row r="11">
@@ -1854,212 +1854,88 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>302.39</v>
+        <v>18.94</v>
       </c>
       <c r="J11" t="n">
-        <v>308.44</v>
+        <v>18.94</v>
       </c>
       <c r="K11" t="n">
-        <v>314.49</v>
+        <v>18.94</v>
       </c>
       <c r="L11" t="n">
-        <v>320.54</v>
+        <v>18.94</v>
       </c>
       <c r="M11" t="n">
-        <v>326.58</v>
+        <v>18.94</v>
       </c>
       <c r="N11" t="n">
-        <v>332.63</v>
+        <v>18.94</v>
       </c>
       <c r="O11" t="n">
-        <v>338.68</v>
+        <v>18.94</v>
       </c>
       <c r="P11" t="n">
-        <v>344.73</v>
+        <v>18.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>350.78</v>
+        <v>26.1</v>
       </c>
       <c r="R11" t="n">
-        <v>356.82</v>
+        <v>33.26</v>
       </c>
       <c r="S11" t="n">
-        <v>362.87</v>
+        <v>40.42</v>
       </c>
       <c r="T11" t="n">
-        <v>368.92</v>
+        <v>47.58</v>
       </c>
       <c r="U11" t="n">
-        <v>374.97</v>
+        <v>54.74</v>
       </c>
       <c r="V11" t="n">
-        <v>381.01</v>
+        <v>63.84</v>
       </c>
       <c r="W11" t="n">
-        <v>387.06</v>
+        <v>72.94</v>
       </c>
       <c r="X11" t="n">
-        <v>393.11</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>399.16</v>
+        <v>91.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>405.21</v>
+        <v>100.24</v>
       </c>
       <c r="AA11" t="n">
-        <v>411.25</v>
+        <v>110.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>417.3</v>
+        <v>120.27</v>
       </c>
       <c r="AC11" t="n">
-        <v>423.35</v>
+        <v>130.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>429.4</v>
+        <v>140.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>435.45</v>
+        <v>150.31</v>
       </c>
       <c r="AF11" t="n">
-        <v>441.49</v>
+        <v>161.31</v>
       </c>
       <c r="AG11" t="n">
-        <v>447.54</v>
+        <v>172.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>453.59</v>
+        <v>183.29</v>
       </c>
       <c r="AI11" t="n">
-        <v>459.64</v>
+        <v>194.29</v>
       </c>
       <c r="AJ11" t="n">
-        <v>465.68</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ELCINDXX02</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Output demand of transmission lines in India</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>not needed</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>not needed</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>not needed</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>User defined</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="J12" t="n">
-        <v>43.94</v>
-      </c>
-      <c r="K12" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>45.66</v>
-      </c>
-      <c r="M12" t="n">
-        <v>46.53</v>
-      </c>
-      <c r="N12" t="n">
-        <v>47.39</v>
-      </c>
-      <c r="O12" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="P12" t="n">
-        <v>49.11</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>49.97</v>
-      </c>
-      <c r="R12" t="n">
-        <v>50.83</v>
-      </c>
-      <c r="S12" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>52.56</v>
-      </c>
-      <c r="U12" t="n">
-        <v>53.42</v>
-      </c>
-      <c r="V12" t="n">
-        <v>54.28</v>
-      </c>
-      <c r="W12" t="n">
-        <v>55.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>56</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>56.87</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>57.73</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>58.59</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>59.45</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>60.31</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>61.17</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>62.03</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>63.76</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>64.62</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>65.48</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>66.34</v>
+        <v>205.28</v>
       </c>
     </row>
   </sheetData>
@@ -2566,88 +2442,88 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
     </row>
     <row r="5">
@@ -2695,88 +2571,88 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="6">
@@ -3082,88 +2958,88 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="9">
@@ -3469,88 +3345,88 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="12">
@@ -3985,88 +3861,88 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="16">
@@ -4243,88 +4119,88 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
     </row>
     <row r="18">
@@ -4372,88 +4248,88 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
     </row>
     <row r="19">
@@ -4759,88 +4635,88 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="W21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
     </row>
     <row r="22">
@@ -5146,88 +5022,88 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="K24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="L24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="M24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="N24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="O24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="P24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="R24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="S24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="T24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="U24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="V24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="W24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="X24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
     </row>
     <row r="25">
@@ -5275,88 +5151,88 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="V25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="W25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="26">
@@ -6049,88 +5925,88 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="32">
@@ -6436,88 +6312,88 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="O34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="T34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="U34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="V34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="W34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="X34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
     </row>
     <row r="35">
@@ -6565,88 +6441,88 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="36">
@@ -6952,88 +6828,88 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="39">
@@ -7726,88 +7602,88 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="L44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="O44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="T44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="V44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="W44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="X44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
     </row>
     <row r="45">
@@ -7855,88 +7731,88 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="46">
@@ -8113,88 +7989,88 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="L47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="N47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="P47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="T47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="U47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="V47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="W47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="X47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
     </row>
     <row r="48">
@@ -8242,88 +8118,88 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="L48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="N48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="O48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="P48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="R48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="T48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="U48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="V48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="W48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="X48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
     </row>
     <row r="49">
@@ -8629,88 +8505,88 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK51" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="52">
@@ -10306,88 +10182,88 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="L64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="M64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="N64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="O64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="P64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="T64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="U64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="V64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="W64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="X64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Z64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AC64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AE64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AF64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AH64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AI64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AK64" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
     </row>
     <row r="65">
@@ -10435,88 +10311,88 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK65" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="66">
@@ -10693,88 +10569,88 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="K67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="L67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="M67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="N67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="O67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="R67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="T67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="U67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="V67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="W67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="Z67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AC67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AE67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AF67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AH67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AI67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AK67" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
     </row>
     <row r="68">
@@ -10822,88 +10698,88 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK68" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="69">
@@ -11596,88 +11472,88 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="L74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="M74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="N74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="O74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="P74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="R74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="T74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="U74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="V74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="W74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="X74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Z74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AC74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AE74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AF74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AH74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AI74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AK74" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
     </row>
     <row r="75">
@@ -11725,88 +11601,88 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK75" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="76">
@@ -11983,88 +11859,88 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="L77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="M77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="N77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="O77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="P77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="T77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="U77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="V77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="W77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="X77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Z77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AC77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AE77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AF77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AH77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AK77" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
     </row>
     <row r="78">
@@ -12112,88 +11988,88 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="K78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="M78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="N78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="O78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="P78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="T78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="U78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="V78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="W78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="X78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Z78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AC78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AF78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AH78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AI78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AK78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
     </row>
     <row r="79">
@@ -12499,88 +12375,88 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK81" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="82">
@@ -14176,88 +14052,88 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="K94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="L94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="M94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="N94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="O94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="P94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="R94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="S94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="T94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="U94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="V94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="W94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="X94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Z94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AA94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AB94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AC94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AD94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AE94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AF94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AG94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AH94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AI94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AK94" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
     </row>
     <row r="95">
@@ -14305,88 +14181,88 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK95" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="96">
@@ -14563,88 +14439,88 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="K97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="L97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="M97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="N97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="O97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="P97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="R97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="S97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="T97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="U97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="V97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="W97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="X97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="Y97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="Z97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AA97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AB97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AC97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AD97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AE97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AF97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AG97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AH97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AI97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AJ97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AK97" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
     </row>
     <row r="98">
@@ -14692,88 +14568,88 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="L98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="M98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="N98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="O98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="P98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="R98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="S98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="V98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="W98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="X98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Z98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AA98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AB98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AC98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AD98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AE98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AF98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AG98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AH98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AI98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AK98" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="99">
@@ -15079,88 +14955,88 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK101" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="102">
@@ -15466,88 +15342,88 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="K104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="L104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="M104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="N104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="O104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="P104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="R104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="S104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="T104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="U104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="V104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="W104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="X104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Y104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Z104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AA104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AB104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AC104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AD104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AE104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AF104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AG104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AH104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AI104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AK104" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
     </row>
     <row r="105">
@@ -15595,88 +15471,88 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK105" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="106">
@@ -15853,88 +15729,88 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="K107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="L107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="M107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="N107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="O107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="P107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="R107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="S107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="T107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="U107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="V107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="W107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="X107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Y107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Z107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AA107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AB107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AC107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AD107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AE107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AF107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AG107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AH107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AI107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AK107" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
     </row>
     <row r="108">
@@ -15982,88 +15858,88 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK108" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="109">
@@ -16369,88 +16245,88 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="K111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="L111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="M111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="N111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="O111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="P111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="R111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="S111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="T111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="U111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="V111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="W111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="X111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Y111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Z111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AA111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AB111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AC111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AD111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AE111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AF111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AG111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AH111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AI111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AK111" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
     </row>
     <row r="112">
@@ -16756,88 +16632,88 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="K114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="L114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="M114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="N114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="O114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="P114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="R114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="S114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="T114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="U114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="V114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="W114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="X114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="Y114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="Z114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AA114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AB114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AC114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AD114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AE114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AF114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AG114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AH114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AI114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AJ114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AK114" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
     </row>
     <row r="115">
@@ -17659,88 +17535,88 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK121" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
   </sheetData>

--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_Demand.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_Demand.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.85546875" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -750,88 +750,88 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>469.23</v>
+        <v>499.71</v>
       </c>
       <c r="J2" t="n">
-        <v>478.61</v>
+        <v>542.73</v>
       </c>
       <c r="K2" t="n">
-        <v>488</v>
+        <v>585.75</v>
       </c>
       <c r="L2" t="n">
-        <v>497.38</v>
+        <v>631.35</v>
       </c>
       <c r="M2" t="n">
-        <v>506.77</v>
+        <v>676.95</v>
       </c>
       <c r="N2" t="n">
-        <v>516.15</v>
+        <v>722.54</v>
       </c>
       <c r="O2" t="n">
-        <v>525.54</v>
+        <v>768.14</v>
       </c>
       <c r="P2" t="n">
-        <v>534.92</v>
+        <v>813.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>544.3099999999999</v>
+        <v>860.42</v>
       </c>
       <c r="R2" t="n">
-        <v>553.6900000000001</v>
+        <v>907.11</v>
       </c>
       <c r="S2" t="n">
-        <v>563.08</v>
+        <v>953.79</v>
       </c>
       <c r="T2" t="n">
-        <v>572.46</v>
+        <v>1000.48</v>
       </c>
       <c r="U2" t="n">
-        <v>581.85</v>
+        <v>1047.16</v>
       </c>
       <c r="V2" t="n">
-        <v>591.23</v>
+        <v>1094.98</v>
       </c>
       <c r="W2" t="n">
-        <v>600.61</v>
+        <v>1142.8</v>
       </c>
       <c r="X2" t="n">
-        <v>610</v>
+        <v>1190.62</v>
       </c>
       <c r="Y2" t="n">
-        <v>619.38</v>
+        <v>1238.44</v>
       </c>
       <c r="Z2" t="n">
-        <v>628.77</v>
+        <v>1286.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>638.15</v>
+        <v>1334.01</v>
       </c>
       <c r="AB2" t="n">
-        <v>647.54</v>
+        <v>1381.76</v>
       </c>
       <c r="AC2" t="n">
-        <v>656.92</v>
+        <v>1429.51</v>
       </c>
       <c r="AD2" t="n">
-        <v>666.3099999999999</v>
+        <v>1477.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>675.6900000000001</v>
+        <v>1525.02</v>
       </c>
       <c r="AF2" t="n">
-        <v>685.08</v>
+        <v>1574.01</v>
       </c>
       <c r="AG2" t="n">
-        <v>694.46</v>
+        <v>1623.01</v>
       </c>
       <c r="AH2" t="n">
-        <v>703.85</v>
+        <v>1672</v>
       </c>
       <c r="AI2" t="n">
-        <v>713.23</v>
+        <v>1721</v>
       </c>
       <c r="AJ2" t="n">
-        <v>722.61</v>
+        <v>1769.99</v>
       </c>
     </row>
     <row r="3">
@@ -874,88 +874,88 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3.87</v>
+        <v>12.58</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>14.11</v>
       </c>
       <c r="K3" t="n">
-        <v>4.03</v>
+        <v>15.66</v>
       </c>
       <c r="L3" t="n">
-        <v>4.11</v>
+        <v>17.32</v>
       </c>
       <c r="M3" t="n">
-        <v>4.18</v>
+        <v>18.97</v>
       </c>
       <c r="N3" t="n">
-        <v>4.26</v>
+        <v>20.62</v>
       </c>
       <c r="O3" t="n">
-        <v>4.34</v>
+        <v>22.27</v>
       </c>
       <c r="P3" t="n">
-        <v>4.42</v>
+        <v>23.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.49</v>
+        <v>25.73</v>
       </c>
       <c r="R3" t="n">
-        <v>4.57</v>
+        <v>27.51</v>
       </c>
       <c r="S3" t="n">
-        <v>4.65</v>
+        <v>29.28</v>
       </c>
       <c r="T3" t="n">
-        <v>4.73</v>
+        <v>31.09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.8</v>
+        <v>32.86</v>
       </c>
       <c r="V3" t="n">
-        <v>4.88</v>
+        <v>34.84</v>
       </c>
       <c r="W3" t="n">
-        <v>4.96</v>
+        <v>36.82</v>
       </c>
       <c r="X3" t="n">
-        <v>5.04</v>
+        <v>38.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.11</v>
+        <v>40.78</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.19</v>
+        <v>42.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.27</v>
+        <v>44.93</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.35</v>
+        <v>47.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.42</v>
+        <v>49.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.5</v>
+        <v>51.47</v>
       </c>
       <c r="AE3" t="n">
-        <v>5.58</v>
+        <v>53.64</v>
       </c>
       <c r="AF3" t="n">
-        <v>5.66</v>
+        <v>56</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.73</v>
+        <v>58.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>5.81</v>
+        <v>60.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.89</v>
+        <v>63.06</v>
       </c>
       <c r="AJ3" t="n">
-        <v>5.97</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="4">
@@ -998,88 +998,88 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>43.08</v>
+        <v>717.27</v>
       </c>
       <c r="J4" t="n">
-        <v>43.94</v>
+        <v>772.87</v>
       </c>
       <c r="K4" t="n">
-        <v>44.8</v>
+        <v>954.61</v>
       </c>
       <c r="L4" t="n">
-        <v>45.66</v>
+        <v>981.6</v>
       </c>
       <c r="M4" t="n">
-        <v>46.53</v>
+        <v>1012.38</v>
       </c>
       <c r="N4" t="n">
-        <v>47.39</v>
+        <v>1043.24</v>
       </c>
       <c r="O4" t="n">
-        <v>48.25</v>
+        <v>1074.44</v>
       </c>
       <c r="P4" t="n">
-        <v>49.11</v>
+        <v>1105.41</v>
       </c>
       <c r="Q4" t="n">
-        <v>49.97</v>
+        <v>1174.28</v>
       </c>
       <c r="R4" t="n">
-        <v>50.83</v>
+        <v>1243.48</v>
       </c>
       <c r="S4" t="n">
-        <v>51.7</v>
+        <v>1314.83</v>
       </c>
       <c r="T4" t="n">
-        <v>52.56</v>
+        <v>1381.43</v>
       </c>
       <c r="U4" t="n">
-        <v>53.42</v>
+        <v>1450.11</v>
       </c>
       <c r="V4" t="n">
-        <v>54.28</v>
+        <v>1531.14</v>
       </c>
       <c r="W4" t="n">
-        <v>55.14</v>
+        <v>1612.66</v>
       </c>
       <c r="X4" t="n">
-        <v>56</v>
+        <v>1693.49</v>
       </c>
       <c r="Y4" t="n">
-        <v>56.87</v>
+        <v>1771</v>
       </c>
       <c r="Z4" t="n">
-        <v>57.73</v>
+        <v>1847.47</v>
       </c>
       <c r="AA4" t="n">
-        <v>58.59</v>
+        <v>1935.51</v>
       </c>
       <c r="AB4" t="n">
-        <v>59.45</v>
+        <v>2025.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>60.31</v>
+        <v>2114.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>61.17</v>
+        <v>2202.04</v>
       </c>
       <c r="AE4" t="n">
-        <v>62.03</v>
+        <v>2289.82</v>
       </c>
       <c r="AF4" t="n">
-        <v>62.9</v>
+        <v>2400.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>63.76</v>
+        <v>2502.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>64.62</v>
+        <v>2603.44</v>
       </c>
       <c r="AI4" t="n">
-        <v>65.48</v>
+        <v>2704.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>66.34</v>
+        <v>2805.83</v>
       </c>
     </row>
     <row r="5">
@@ -1122,88 +1122,88 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>43.08</v>
+        <v>145.19</v>
       </c>
       <c r="J5" t="n">
-        <v>43.94</v>
+        <v>157.09</v>
       </c>
       <c r="K5" t="n">
-        <v>44.8</v>
+        <v>195.14</v>
       </c>
       <c r="L5" t="n">
-        <v>45.66</v>
+        <v>201.8</v>
       </c>
       <c r="M5" t="n">
-        <v>46.53</v>
+        <v>208.75</v>
       </c>
       <c r="N5" t="n">
-        <v>47.39</v>
+        <v>215.73</v>
       </c>
       <c r="O5" t="n">
-        <v>48.25</v>
+        <v>222.8</v>
       </c>
       <c r="P5" t="n">
-        <v>49.11</v>
+        <v>229.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>49.97</v>
+        <v>244.87</v>
       </c>
       <c r="R5" t="n">
-        <v>50.83</v>
+        <v>259.92</v>
       </c>
       <c r="S5" t="n">
-        <v>51.7</v>
+        <v>274.7</v>
       </c>
       <c r="T5" t="n">
-        <v>52.56</v>
+        <v>289.36</v>
       </c>
       <c r="U5" t="n">
-        <v>53.42</v>
+        <v>304.15</v>
       </c>
       <c r="V5" t="n">
-        <v>54.28</v>
+        <v>320.97</v>
       </c>
       <c r="W5" t="n">
-        <v>55.14</v>
+        <v>337.64</v>
       </c>
       <c r="X5" t="n">
-        <v>56</v>
+        <v>354.26</v>
       </c>
       <c r="Y5" t="n">
-        <v>56.87</v>
+        <v>371.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>57.73</v>
+        <v>387.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>58.59</v>
+        <v>406.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>59.45</v>
+        <v>424.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>60.31</v>
+        <v>443.96</v>
       </c>
       <c r="AD5" t="n">
-        <v>61.17</v>
+        <v>463.54</v>
       </c>
       <c r="AE5" t="n">
-        <v>62.03</v>
+        <v>482.69</v>
       </c>
       <c r="AF5" t="n">
-        <v>62.9</v>
+        <v>505.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>63.76</v>
+        <v>527.41</v>
       </c>
       <c r="AH5" t="n">
-        <v>64.62</v>
+        <v>548.9299999999999</v>
       </c>
       <c r="AI5" t="n">
-        <v>65.48</v>
+        <v>570.39</v>
       </c>
       <c r="AJ5" t="n">
-        <v>66.34</v>
+        <v>591.8200000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1246,88 +1246,88 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>43.08</v>
+        <v>1490.33</v>
       </c>
       <c r="J6" t="n">
-        <v>43.94</v>
+        <v>1607.32</v>
       </c>
       <c r="K6" t="n">
-        <v>44.8</v>
+        <v>1983.05</v>
       </c>
       <c r="L6" t="n">
-        <v>45.66</v>
+        <v>2046.01</v>
       </c>
       <c r="M6" t="n">
-        <v>46.53</v>
+        <v>2110.99</v>
       </c>
       <c r="N6" t="n">
-        <v>47.39</v>
+        <v>2175.99</v>
       </c>
       <c r="O6" t="n">
-        <v>48.25</v>
+        <v>2240.57</v>
       </c>
       <c r="P6" t="n">
-        <v>49.11</v>
+        <v>2304.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>49.97</v>
+        <v>2445.12</v>
       </c>
       <c r="R6" t="n">
-        <v>50.83</v>
+        <v>2584.15</v>
       </c>
       <c r="S6" t="n">
-        <v>51.7</v>
+        <v>2722.59</v>
       </c>
       <c r="T6" t="n">
-        <v>52.56</v>
+        <v>2862.69</v>
       </c>
       <c r="U6" t="n">
-        <v>53.42</v>
+        <v>3002.82</v>
       </c>
       <c r="V6" t="n">
-        <v>54.28</v>
+        <v>3167.14</v>
       </c>
       <c r="W6" t="n">
-        <v>55.14</v>
+        <v>3331.72</v>
       </c>
       <c r="X6" t="n">
-        <v>56</v>
+        <v>3495.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>56.87</v>
+        <v>3661.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>57.73</v>
+        <v>3825.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>58.59</v>
+        <v>4014.42</v>
       </c>
       <c r="AB6" t="n">
-        <v>59.45</v>
+        <v>4200.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>60.31</v>
+        <v>4384.46</v>
       </c>
       <c r="AD6" t="n">
-        <v>61.17</v>
+        <v>4564.84</v>
       </c>
       <c r="AE6" t="n">
-        <v>62.03</v>
+        <v>4744.94</v>
       </c>
       <c r="AF6" t="n">
-        <v>62.9</v>
+        <v>4968.31</v>
       </c>
       <c r="AG6" t="n">
-        <v>63.76</v>
+        <v>5176.61</v>
       </c>
       <c r="AH6" t="n">
-        <v>64.62</v>
+        <v>5384.83</v>
       </c>
       <c r="AI6" t="n">
-        <v>65.48</v>
+        <v>5593.11</v>
       </c>
       <c r="AJ6" t="n">
-        <v>66.34</v>
+        <v>5801.69</v>
       </c>
     </row>
     <row r="7">
@@ -1370,88 +1370,88 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>43.08</v>
+        <v>1677.48</v>
       </c>
       <c r="J7" t="n">
-        <v>43.94</v>
+        <v>1819.57</v>
       </c>
       <c r="K7" t="n">
-        <v>44.8</v>
+        <v>2261.9</v>
       </c>
       <c r="L7" t="n">
-        <v>45.66</v>
+        <v>2350.89</v>
       </c>
       <c r="M7" t="n">
-        <v>46.53</v>
+        <v>2430.09</v>
       </c>
       <c r="N7" t="n">
-        <v>47.39</v>
+        <v>2508.94</v>
       </c>
       <c r="O7" t="n">
-        <v>48.25</v>
+        <v>2588.21</v>
       </c>
       <c r="P7" t="n">
-        <v>49.11</v>
+        <v>2668.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>49.97</v>
+        <v>2837.62</v>
       </c>
       <c r="R7" t="n">
-        <v>50.83</v>
+        <v>3009.7</v>
       </c>
       <c r="S7" t="n">
-        <v>51.7</v>
+        <v>3181.67</v>
       </c>
       <c r="T7" t="n">
-        <v>52.56</v>
+        <v>3352.73</v>
       </c>
       <c r="U7" t="n">
-        <v>53.42</v>
+        <v>3524.68</v>
       </c>
       <c r="V7" t="n">
-        <v>54.28</v>
+        <v>3722.05</v>
       </c>
       <c r="W7" t="n">
-        <v>55.14</v>
+        <v>3918.08</v>
       </c>
       <c r="X7" t="n">
-        <v>56</v>
+        <v>4114.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>56.87</v>
+        <v>4310.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>57.73</v>
+        <v>4504.27</v>
       </c>
       <c r="AA7" t="n">
-        <v>58.59</v>
+        <v>4726.24</v>
       </c>
       <c r="AB7" t="n">
-        <v>59.45</v>
+        <v>4948.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>60.31</v>
+        <v>5170.39</v>
       </c>
       <c r="AD7" t="n">
-        <v>61.17</v>
+        <v>5393.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>62.03</v>
+        <v>5615.87</v>
       </c>
       <c r="AF7" t="n">
-        <v>62.9</v>
+        <v>5881.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>63.76</v>
+        <v>6132.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>64.62</v>
+        <v>6383.02</v>
       </c>
       <c r="AI7" t="n">
-        <v>65.48</v>
+        <v>6633.32</v>
       </c>
       <c r="AJ7" t="n">
-        <v>66.34</v>
+        <v>6883.89</v>
       </c>
     </row>
     <row r="8">
@@ -1494,88 +1494,88 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>43.08</v>
+        <v>1429.56</v>
       </c>
       <c r="J8" t="n">
-        <v>43.94</v>
+        <v>1546.72</v>
       </c>
       <c r="K8" t="n">
-        <v>44.8</v>
+        <v>1924.8</v>
       </c>
       <c r="L8" t="n">
-        <v>45.66</v>
+        <v>1984.31</v>
       </c>
       <c r="M8" t="n">
-        <v>46.53</v>
+        <v>2047.52</v>
       </c>
       <c r="N8" t="n">
-        <v>47.39</v>
+        <v>2110.93</v>
       </c>
       <c r="O8" t="n">
-        <v>48.25</v>
+        <v>2173.93</v>
       </c>
       <c r="P8" t="n">
-        <v>49.11</v>
+        <v>2236.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>49.97</v>
+        <v>2377.13</v>
       </c>
       <c r="R8" t="n">
-        <v>50.83</v>
+        <v>2515.72</v>
       </c>
       <c r="S8" t="n">
-        <v>51.7</v>
+        <v>2653.12</v>
       </c>
       <c r="T8" t="n">
-        <v>52.56</v>
+        <v>2794.64</v>
       </c>
       <c r="U8" t="n">
-        <v>53.42</v>
+        <v>2933.03</v>
       </c>
       <c r="V8" t="n">
-        <v>54.28</v>
+        <v>3097.73</v>
       </c>
       <c r="W8" t="n">
-        <v>55.14</v>
+        <v>3263.16</v>
       </c>
       <c r="X8" t="n">
-        <v>56</v>
+        <v>3429.97</v>
       </c>
       <c r="Y8" t="n">
-        <v>56.87</v>
+        <v>3598.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>57.73</v>
+        <v>3770.82</v>
       </c>
       <c r="AA8" t="n">
-        <v>58.59</v>
+        <v>3967.13</v>
       </c>
       <c r="AB8" t="n">
-        <v>59.45</v>
+        <v>4164.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>60.31</v>
+        <v>4363.59</v>
       </c>
       <c r="AD8" t="n">
-        <v>61.17</v>
+        <v>4567.55</v>
       </c>
       <c r="AE8" t="n">
-        <v>62.03</v>
+        <v>4771.66</v>
       </c>
       <c r="AF8" t="n">
-        <v>62.9</v>
+        <v>4944.69</v>
       </c>
       <c r="AG8" t="n">
-        <v>63.76</v>
+        <v>5158.53</v>
       </c>
       <c r="AH8" t="n">
-        <v>64.62</v>
+        <v>5372.85</v>
       </c>
       <c r="AI8" t="n">
-        <v>65.48</v>
+        <v>5587.59</v>
       </c>
       <c r="AJ8" t="n">
-        <v>66.34</v>
+        <v>5801.92</v>
       </c>
     </row>
     <row r="9">
@@ -1618,88 +1618,88 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>290.09</v>
+        <v>47.48</v>
       </c>
       <c r="J9" t="n">
-        <v>295.89</v>
+        <v>47.48</v>
       </c>
       <c r="K9" t="n">
-        <v>301.69</v>
+        <v>47.48</v>
       </c>
       <c r="L9" t="n">
-        <v>307.49</v>
+        <v>54.22</v>
       </c>
       <c r="M9" t="n">
-        <v>313.3</v>
+        <v>60.95</v>
       </c>
       <c r="N9" t="n">
-        <v>319.1</v>
+        <v>67.69</v>
       </c>
       <c r="O9" t="n">
-        <v>324.9</v>
+        <v>74.42</v>
       </c>
       <c r="P9" t="n">
-        <v>330.7</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>336.5</v>
+        <v>88.8</v>
       </c>
       <c r="R9" t="n">
-        <v>342.31</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>348.11</v>
+        <v>104.11</v>
       </c>
       <c r="T9" t="n">
-        <v>353.91</v>
+        <v>111.76</v>
       </c>
       <c r="U9" t="n">
-        <v>359.71</v>
+        <v>119.41</v>
       </c>
       <c r="V9" t="n">
-        <v>365.51</v>
+        <v>127.6</v>
       </c>
       <c r="W9" t="n">
-        <v>371.31</v>
+        <v>135.78</v>
       </c>
       <c r="X9" t="n">
-        <v>377.12</v>
+        <v>143.96</v>
       </c>
       <c r="Y9" t="n">
-        <v>382.92</v>
+        <v>152.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>388.72</v>
+        <v>160.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>394.52</v>
+        <v>168.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>400.32</v>
+        <v>177.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>406.13</v>
+        <v>186.23</v>
       </c>
       <c r="AD9" t="n">
-        <v>411.93</v>
+        <v>194.87</v>
       </c>
       <c r="AE9" t="n">
-        <v>417.73</v>
+        <v>203.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>423.53</v>
+        <v>212.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>429.33</v>
+        <v>221.7</v>
       </c>
       <c r="AH9" t="n">
-        <v>435.13</v>
+        <v>230.79</v>
       </c>
       <c r="AI9" t="n">
-        <v>440.94</v>
+        <v>239.89</v>
       </c>
       <c r="AJ9" t="n">
-        <v>446.74</v>
+        <v>248.99</v>
       </c>
     </row>
     <row r="10">
@@ -1742,212 +1742,88 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>302.39</v>
+        <v>18.94</v>
       </c>
       <c r="J10" t="n">
-        <v>308.44</v>
+        <v>18.94</v>
       </c>
       <c r="K10" t="n">
-        <v>314.49</v>
+        <v>18.94</v>
       </c>
       <c r="L10" t="n">
-        <v>320.54</v>
+        <v>18.94</v>
       </c>
       <c r="M10" t="n">
-        <v>326.58</v>
+        <v>18.94</v>
       </c>
       <c r="N10" t="n">
-        <v>332.63</v>
+        <v>18.94</v>
       </c>
       <c r="O10" t="n">
-        <v>338.68</v>
+        <v>18.94</v>
       </c>
       <c r="P10" t="n">
-        <v>344.73</v>
+        <v>18.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>350.78</v>
+        <v>26.1</v>
       </c>
       <c r="R10" t="n">
-        <v>356.82</v>
+        <v>33.26</v>
       </c>
       <c r="S10" t="n">
-        <v>362.87</v>
+        <v>40.42</v>
       </c>
       <c r="T10" t="n">
-        <v>368.92</v>
+        <v>47.58</v>
       </c>
       <c r="U10" t="n">
-        <v>374.97</v>
+        <v>54.74</v>
       </c>
       <c r="V10" t="n">
-        <v>381.01</v>
+        <v>63.84</v>
       </c>
       <c r="W10" t="n">
-        <v>387.06</v>
+        <v>72.94</v>
       </c>
       <c r="X10" t="n">
-        <v>393.11</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>399.16</v>
+        <v>91.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>405.21</v>
+        <v>100.24</v>
       </c>
       <c r="AA10" t="n">
-        <v>411.25</v>
+        <v>110.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>417.3</v>
+        <v>120.27</v>
       </c>
       <c r="AC10" t="n">
-        <v>423.35</v>
+        <v>130.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>429.4</v>
+        <v>140.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>435.45</v>
+        <v>150.31</v>
       </c>
       <c r="AF10" t="n">
-        <v>441.49</v>
+        <v>161.31</v>
       </c>
       <c r="AG10" t="n">
-        <v>447.54</v>
+        <v>172.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>453.59</v>
+        <v>183.29</v>
       </c>
       <c r="AI10" t="n">
-        <v>459.64</v>
+        <v>194.29</v>
       </c>
       <c r="AJ10" t="n">
-        <v>465.68</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ELCMDVXX03</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Output demand of dispatch-ready in Maldives</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>not needed</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>not needed</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>not needed</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>User defined</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2549.23</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2600.21</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2651.2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2702.18</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2753.17</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2804.15</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2855.14</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2906.12</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2957.11</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3008.09</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3059.07</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3110.06</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3161.04</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3212.03</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3263.01</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3314</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>3364.98</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3415.97</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3466.95</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>3517.94</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3568.92</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3619.91</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>3670.89</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>3721.87</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3772.86</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3823.84</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>3874.83</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>3925.81</v>
+        <v>205.28</v>
       </c>
     </row>
   </sheetData>
@@ -2454,88 +2330,88 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
     </row>
     <row r="5">
@@ -2583,88 +2459,88 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="6">
@@ -2970,88 +2846,88 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="9">
@@ -3228,88 +3104,88 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="11">
@@ -3744,88 +3620,88 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="15">
@@ -4002,88 +3878,88 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
     </row>
     <row r="17">
@@ -4131,88 +4007,88 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
     </row>
     <row r="18">
@@ -4389,88 +4265,88 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="W19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.05050505050505051</v>
       </c>
     </row>
     <row r="20">
@@ -4776,88 +4652,88 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="K22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="L22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="M22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="N22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="O22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="P22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="R22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="S22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="T22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="U22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="V22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="W22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="X22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
     </row>
     <row r="23">
@@ -4905,88 +4781,88 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="W23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="24">
@@ -5550,88 +5426,88 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="29">
@@ -5937,88 +5813,88 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="T31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="U31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="V31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="W31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="X31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
     </row>
     <row r="32">
@@ -6066,88 +5942,88 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="33">
@@ -6453,88 +6329,88 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="36">
@@ -7098,88 +6974,88 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="M40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="O40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="P40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="T40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="U40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="V40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="W40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="X40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
     </row>
     <row r="41">
@@ -7227,88 +7103,88 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="42">
@@ -7485,88 +7361,88 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="L43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="M43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="N43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="O43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="S43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="T43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="U43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="V43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="W43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="X43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
     </row>
     <row r="44">
@@ -7614,88 +7490,88 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="L44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="O44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="T44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="V44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="W44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="X44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
     </row>
     <row r="45">
@@ -7872,88 +7748,88 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="47">
@@ -9420,88 +9296,88 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="K58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="L58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="N58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="O58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="P58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="R58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="T58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="U58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="V58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="W58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="X58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AC58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AI58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AK58" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
     </row>
     <row r="59">
@@ -9549,88 +9425,88 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK59" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="60">
@@ -9807,88 +9683,88 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="K61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="L61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="N61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="O61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="P61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="T61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="U61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="V61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="W61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="X61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AC61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AE61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AH61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AI61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AK61" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
     </row>
     <row r="62">
@@ -9936,88 +9812,88 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK62" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="63">
@@ -10581,88 +10457,88 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="K67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="L67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="M67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="N67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="O67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="R67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="T67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="U67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="V67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="W67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Z67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AC67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AE67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AF67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AH67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AI67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AK67" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
     </row>
     <row r="68">
@@ -10710,88 +10586,88 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK68" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="69">
@@ -10968,88 +10844,88 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="K70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="L70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="M70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="N70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="O70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="P70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="R70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="T70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="U70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="V70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="W70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="X70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Z70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AC70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AE70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AF70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AH70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AI70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AK70" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
     </row>
     <row r="71">
@@ -11097,88 +10973,88 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="K71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="L71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="M71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="N71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="O71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="P71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="R71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="T71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="U71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="V71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="W71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="X71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AC71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AE71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AF71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AH71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AK71" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
     </row>
     <row r="72">
@@ -11355,88 +11231,88 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK73" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="74">
@@ -12903,88 +12779,88 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="K85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="L85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="M85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="N85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="O85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="P85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="R85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="T85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="U85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="V85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="W85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="X85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Y85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="Z85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AB85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AC85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AE85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AF85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AH85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AI85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="AK85" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.07920792079207921</v>
       </c>
     </row>
     <row r="86">
@@ -13032,88 +12908,88 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK86" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
     <row r="87">
@@ -13290,88 +13166,88 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="K88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="L88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="M88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="N88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="O88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="R88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="T88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="U88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="V88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="W88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="X88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="Z88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AB88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AC88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AE88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AF88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AH88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AI88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
       <c r="AK88" t="n">
-        <v>0.0918367346938775</v>
+        <v>0.09183673469387756</v>
       </c>
     </row>
     <row r="89">
@@ -13419,88 +13295,88 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="K89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="L89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="M89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="N89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="O89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="P89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="R89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="T89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="V89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="W89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="X89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Y89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Z89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AB89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AC89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AE89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AF89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AH89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AI89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AK89" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="90">
@@ -13677,88 +13553,88 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK91" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="92">
@@ -14064,88 +13940,88 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="K94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="L94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="M94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="N94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="O94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="P94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="R94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="S94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="T94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="U94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="V94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="W94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="X94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="Z94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AA94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AB94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AC94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AD94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AE94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AF94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AG94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AH94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AI94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AK94" t="n">
-        <v>0.0693069306930693</v>
+        <v>0.06930693069306931</v>
       </c>
     </row>
     <row r="95">
@@ -14193,88 +14069,88 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK95" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="96">
@@ -14451,88 +14327,88 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="K97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="L97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="M97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="N97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="O97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="P97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="R97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="S97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="T97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="U97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="V97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="W97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="X97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Y97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="Z97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AA97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AB97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AC97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AD97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AE97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AF97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AG97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AH97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AI97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AJ97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AK97" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.06122448979591837</v>
       </c>
     </row>
     <row r="98">
@@ -14580,88 +14456,88 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="L98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="M98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="N98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="O98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="R98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="S98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="T98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="U98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="V98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="W98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="X98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="Z98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AA98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AB98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AC98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AD98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AE98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AF98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AG98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AH98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AI98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="AK98" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07070707070707072</v>
       </c>
     </row>
     <row r="99">
@@ -14838,88 +14714,88 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="K100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="L100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="M100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="N100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="O100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="P100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="R100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="S100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="T100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="U100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="V100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="W100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="X100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Y100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Z100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AA100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AB100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AC100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AD100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AE100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AF100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AG100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AH100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AI100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AJ100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AK100" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.06060606060606061</v>
       </c>
     </row>
     <row r="101">
@@ -15225,88 +15101,88 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="K103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="L103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="M103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="N103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="O103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="P103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="R103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="S103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="T103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="U103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="V103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="W103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="X103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="Z103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AA103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AB103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AC103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AD103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AE103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AF103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AG103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AH103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AI103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AJ103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="AK103" t="n">
-        <v>0.099009900990099</v>
+        <v>0.09900990099009901</v>
       </c>
     </row>
     <row r="104">
@@ -15999,88 +15875,88 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="K109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="L109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="M109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="N109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="O109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="P109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="R109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="S109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="T109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="U109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="V109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="W109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="X109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Y109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="Z109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AA109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AB109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AC109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AD109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AE109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AF109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AG109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AH109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AI109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
       <c r="AK109" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.08080808080808081</v>
       </c>
     </row>
   </sheetData>

--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_Demand.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_Demand.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand_Projection" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profiles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Demand_Projection" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Profiles" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>

--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_Demand.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_Demand.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Demand_Projection" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Profiles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand_Projection" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profiles" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
